--- a/maestros/Maestro_Wellpro_borrador.xlsx
+++ b/maestros/Maestro_Wellpro_borrador.xlsx
@@ -3935,7 +3935,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Asignado por EAN calculado del UPC.</t>
+          <t>Asignado por EAN calculado del UPC. En Retail Link su Vendor Stk Nbr es «MTB132FA», no el código del ERP.</t>
         </is>
       </c>
     </row>
